--- a/qa-tests/My ticket website test results.xlsx
+++ b/qa-tests/My ticket website test results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moham\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\Projects\LaraJobs\myticket.sa\qa-tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5FE7AE60-9AD0-4FE2-9FA1-DC1D1E2E63B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{487821F1-4E53-4D7C-8F35-0931F23BEAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Submit Talent/Facility Request Redirects Back to Sign in page</t>
-  </si>
-  <si>
     <t xml:space="preserve">Log in </t>
   </si>
   <si>
@@ -57,9 +54,6 @@
     <t>Both "Submit Talent Request" and "Submit Facility Request" redirect the user back to the "Sign Request" page instead of opening the relevant request form.</t>
   </si>
   <si>
-    <t>Incorrect Language Flag Displayed</t>
-  </si>
-  <si>
     <t>Home</t>
   </si>
   <si>
@@ -74,9 +68,6 @@
     <t>The US flag is displayed while the  website is already in English</t>
   </si>
   <si>
-    <t>Blank white screen displayed and stuck after succesful  sign in until page refresh</t>
-  </si>
-  <si>
     <t>Sign in</t>
   </si>
   <si>
@@ -87,9 +78,6 @@
   </si>
   <si>
     <t>Blank white screen is displayed until user refresh the page</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Blank content area </t>
   </si>
   <si>
     <t>Tickets and offers</t>
@@ -120,9 +108,6 @@
   </si>
   <si>
     <t>The content area appears blank and only become visible after scrolling down.</t>
-  </si>
-  <si>
-    <t>Event not displayed despite search showing one matching result</t>
   </si>
   <si>
     <t>Log in to the MyTicket website.
@@ -188,13 +173,6 @@
     </r>
   </si>
   <si>
-    <t>Talents and Offers pages appear blank until scrolling or navigating back, The same issue happens when I click on Offers ,the page appears blank and I have to scroll down to see the content.
-Interestingly, if I click Back and then open Talents or Offers again, the content appears normally without needing to scroll.</t>
-  </si>
-  <si>
-    <t>Blank white screen displayed and stuck after succesful account creation until page refresh</t>
-  </si>
-  <si>
     <t>Go to MyTicket website. Create account</t>
   </si>
   <si>
@@ -208,12 +186,6 @@
   </si>
   <si>
     <t>Institutions</t>
-  </si>
-  <si>
-    <t>File upload button is unresponsive</t>
-  </si>
-  <si>
-    <t>Support Chat Messages Do Not Appear in Real Time</t>
   </si>
   <si>
     <t>Log in as a user.
@@ -229,9 +201,6 @@
     <t>The chat remains stuck on "Typing…"  and the support reply does not appear for the user until the page is manually refreshed.</t>
   </si>
   <si>
-    <t>Incorrect Support Contact Name Displayed for Ticket</t>
-  </si>
-  <si>
     <t>Click Contact Support.
 Check the name displayed for the support contact.</t>
   </si>
@@ -243,9 +212,6 @@
   </si>
   <si>
     <t>Support chat</t>
-  </si>
-  <si>
-    <t>"End chat" button is unresponsive</t>
   </si>
   <si>
     <r>
@@ -287,9 +253,6 @@
     <t>Go to account and then go to reservations or favorites , click browse events</t>
   </si>
   <si>
-    <t>City filter results disappear immediately</t>
-  </si>
-  <si>
     <t>Go to Search Events.
 Open the City filter.
 Select a city.
@@ -302,9 +265,6 @@
     <t>The filtered event results appear and then disappear immediately</t>
   </si>
   <si>
-    <t>Popular results disappear immediately</t>
-  </si>
-  <si>
     <t>Go to popular under search events , select Ruyadh season</t>
   </si>
   <si>
@@ -315,9 +275,6 @@
   </si>
   <si>
     <t>Checkout</t>
-  </si>
-  <si>
-    <t>Checkout total does not match payment total</t>
   </si>
   <si>
     <t>Select any event and ticket.
@@ -332,14 +289,7 @@
     <t>he payment page displays and processes only the ticket price, excluding the VAT and service fee added at checkout.</t>
   </si>
   <si>
-    <t>Share night button is unresponsive</t>
-  </si>
-  <si>
     <t>Payment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Past events are still available for ticket purchase
-</t>
   </si>
   <si>
     <t>Purchase a ticket for any event.
@@ -365,9 +315,6 @@
     <t>Past events are still displayed with an option to purchase tickets.</t>
   </si>
   <si>
-    <t>Multiple free tickets cannot be assigned to different Names</t>
-  </si>
-  <si>
     <t>Select an event with free tickets
 Select more than one ticket.
 Proceed with the ticket purchase
@@ -378,9 +325,6 @@
   </si>
   <si>
     <t>All purchased tickets are automatically assigned to the user's name, with no option to enter a different name for each ticket.</t>
-  </si>
-  <si>
-    <t>Narrowing results filter is not working</t>
   </si>
   <si>
     <r>
@@ -404,9 +348,6 @@
     <t>The Narrow It Down filter does not work, and the talent results remain unchanged.</t>
   </si>
   <si>
-    <t>Attractions and Activities search filter not Working</t>
-  </si>
-  <si>
     <t>Touristic monuments</t>
   </si>
   <si>
@@ -414,9 +355,6 @@
   </si>
   <si>
     <t>The search filter does not work</t>
-  </si>
-  <si>
-    <t>Host and experience feature still present</t>
   </si>
   <si>
     <t xml:space="preserve">Go to Touristic monuments and click view all </t>
@@ -432,9 +370,6 @@
 Use the search filter</t>
   </si>
   <si>
-    <t>Instagram link not redirecting</t>
-  </si>
-  <si>
     <t>Footer</t>
   </si>
   <si>
@@ -445,9 +380,6 @@
   </si>
   <si>
     <t>Redirects user to page not found</t>
-  </si>
-  <si>
-    <t>Incorrect Phone Number Displayed in Footer</t>
   </si>
   <si>
     <t>Scroll to the bottom of the website.
@@ -462,6 +394,74 @@
   </si>
   <si>
     <t>My ticket website test results 1 ( mac ) 24 / 09 /2026</t>
+  </si>
+  <si>
+    <t>Checkout total does not match payment total *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Past events are still available for ticket purchase *
+</t>
+  </si>
+  <si>
+    <t>Multiple free tickets cannot be assigned to different Names *</t>
+  </si>
+  <si>
+    <t>Instagram link not redirecting @</t>
+  </si>
+  <si>
+    <t>Incorrect Phone Number Displayed in Footer @</t>
+  </si>
+  <si>
+    <t>Attractions and Activities search filter not Working @</t>
+  </si>
+  <si>
+    <t>Incorrect Language Flag Displayed @</t>
+  </si>
+  <si>
+    <t>Blank white screen displayed and stuck after succesful account creation until page refresh @</t>
+  </si>
+  <si>
+    <t>Blank white screen displayed and stuck after succesful  sign in until page  @</t>
+  </si>
+  <si>
+    <t>Blank content area *</t>
+  </si>
+  <si>
+    <t>Event not displayed despite search showing one matching result *</t>
+  </si>
+  <si>
+    <t>Incorrect Support Contact Name Displayed for Ticket @</t>
+  </si>
+  <si>
+    <t>"End chat" button is unresponsive @</t>
+  </si>
+  <si>
+    <t>Share night button is unresponsive @</t>
+  </si>
+  <si>
+    <t>Narrowing results filter is not working @</t>
+  </si>
+  <si>
+    <t>Host and experience feature still present ?</t>
+  </si>
+  <si>
+    <t>Popular results disappear immediately ?</t>
+  </si>
+  <si>
+    <t>File upload button is unresponsive @</t>
+  </si>
+  <si>
+    <t>Submit Talent/Facility Request Redirects Back to Sign in page @</t>
+  </si>
+  <si>
+    <t>Support Chat Messages Do Not Appear in Real Time @</t>
+  </si>
+  <si>
+    <t>Talents and Offers pages appear blank until scrolling or navigating back, The same issue happens when I click on Offers ,the page appears blank and I have to scroll down to see the content.
+Interestingly, if I click Back and then open Talents or Offers again, the content appears normally without needing to scroll. *</t>
+  </si>
+  <si>
+    <t>City filter results disappear immediately *</t>
   </si>
 </sst>
 </file>
@@ -1021,15 +1021,16 @@
   <cols>
     <col min="1" max="1" width="3.77734375" customWidth="1"/>
     <col min="2" max="2" width="23.109375" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="29.77734375" customWidth="1"/>
+    <col min="3" max="3" width="48.77734375" customWidth="1"/>
     <col min="4" max="4" width="14.109375" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="7" width="26" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="61.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="24"/>
@@ -1072,19 +1073,19 @@
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="20" t="s">
+        <v>103</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="F3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="G3" s="20" t="s">
         <v>9</v>
-      </c>
-      <c r="G3" s="20" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="19" customFormat="1" ht="85.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1093,19 +1094,19 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="F4" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="G4" s="20" t="s">
         <v>13</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="20" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:14" s="19" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.3">
@@ -1114,19 +1115,19 @@
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="20" t="s">
-        <v>35</v>
+        <v>92</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F5" s="18" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:14" s="19" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1135,19 +1136,19 @@
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="G6" s="20" t="s">
         <v>17</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="19" customFormat="1" ht="93.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1156,19 +1157,19 @@
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="20" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F7" s="18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:14" s="19" customFormat="1" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,19 +1178,19 @@
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="20" t="s">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F8" s="18" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:14" s="19" customFormat="1" ht="178.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1198,19 +1199,19 @@
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="20" t="s">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="19" customFormat="1" ht="70.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1219,19 +1220,19 @@
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="20" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F10" s="18" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:14" s="19" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
@@ -1240,19 +1241,19 @@
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="20" t="s">
-        <v>42</v>
+        <v>104</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F11" s="18" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14" s="19" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
@@ -1261,19 +1262,19 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="20" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:14" s="19" customFormat="1" ht="98.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1282,19 +1283,19 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="20" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:14" s="19" customFormat="1" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1303,19 +1304,19 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="20" t="s">
-        <v>21</v>
+        <v>94</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:14" s="19" customFormat="1" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -1324,19 +1325,19 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="20" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="1:14" s="19" customFormat="1" ht="86.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1345,19 +1346,19 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="20" t="s">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="19" customFormat="1" ht="111.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1366,19 +1367,19 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="20" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="19" customFormat="1" ht="72.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -1387,19 +1388,19 @@
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="20" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="F18" s="18" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="19" customFormat="1" ht="91.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1408,19 +1409,19 @@
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="20" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="F19" s="18" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>79</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="19" customFormat="1" ht="94.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1429,19 +1430,19 @@
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="20" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="D20" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="G20" s="20" t="s">
         <v>66</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="19" customFormat="1" ht="90.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1450,19 +1451,19 @@
       </c>
       <c r="B21" s="2"/>
       <c r="C21" s="20" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="19" customFormat="1" ht="78" customHeight="1" x14ac:dyDescent="0.3">
@@ -1471,19 +1472,19 @@
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="20" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="19" customFormat="1" ht="63.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -1492,19 +1493,19 @@
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="20" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D23" s="21" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="19" customFormat="1" ht="70.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1513,19 +1514,19 @@
       </c>
       <c r="B24" s="2"/>
       <c r="C24" s="20" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="F24" s="18" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="19" customFormat="1" ht="80.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
@@ -1534,19 +1535,19 @@
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="20" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
       <c r="F25" s="18" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="19" customFormat="1" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
